--- a/TEF/QuLL_TEF_Fund_v6.xlsx
+++ b/TEF/QuLL_TEF_Fund_v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rashap/Documents/Quantum/Quantum/TEF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D776439-80C0-024D-8135-F677A31075D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CABE01B-2786-B14B-AC00-89A319702646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12600" yWindow="1680" windowWidth="25540" windowHeight="16680" xr2:uid="{EB2CBE15-7BB4-DD40-815F-8021B0A65FC3}"/>
+    <workbookView xWindow="1540" yWindow="860" windowWidth="19560" windowHeight="16680" xr2:uid="{EB2CBE15-7BB4-DD40-815F-8021B0A65FC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
   <si>
     <t>TEF Funds UNM Subaward to CNM Ingenuity Budget Breakdown</t>
   </si>
@@ -140,16 +140,13 @@
     <t>Revised TEF Funds UNM Subaward to CNM Ingenuity Budget Breakdown</t>
   </si>
   <si>
-    <t>Additional 24752 in Year 2 and 25248 in Year 3 (2% increase)</t>
-  </si>
-  <si>
     <t>Previous $1812921</t>
   </si>
   <si>
-    <t>Assume 34% fringe on year 2 and 3 adds</t>
-  </si>
-  <si>
     <t>Add $25k each to Yesr 2 and 3</t>
+  </si>
+  <si>
+    <t>Other - Contracted Services (SME/Intern)</t>
   </si>
 </sst>
 </file>
@@ -447,6 +444,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -456,10 +457,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -794,23 +791,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DCBC226-7DF0-DE4B-A584-7AB384523D3D}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="1" max="1" width="35.1640625" customWidth="1"/>
+    <col min="2" max="7" width="8.6640625" customWidth="1"/>
     <col min="8" max="8" width="65.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1185,14 +1183,14 @@
     <row r="18" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="20"/>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="36"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="21"/>
@@ -1467,22 +1465,22 @@
         <f t="shared" ref="G31" si="9">SUM(G22:G30)</f>
         <v>1812920.72010176</v>
       </c>
-      <c r="I31" s="36">
-        <f>G47-G31</f>
+      <c r="I31" s="33">
+        <f>G48-G31</f>
         <v>200000</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="20"/>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="32"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="36"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
@@ -1522,12 +1520,11 @@
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6">
-        <f>78708+I46</f>
-        <v>97179.996453376676</v>
+        <v>78708</v>
       </c>
       <c r="D37" s="6">
-        <f>D22+J46</f>
-        <v>99123.596382444215</v>
+        <f>C37*1.02</f>
+        <v>80282.16</v>
       </c>
       <c r="E37" s="6">
         <f>E22</f>
@@ -1538,8 +1535,8 @@
         <v>83525.55926400001</v>
       </c>
       <c r="G37" s="24">
-        <f t="shared" ref="G37:G46" si="10">SUM(B37:F37)</f>
-        <v>361716.95529982087</v>
+        <f t="shared" ref="G37:G47" si="10">SUM(B37:F37)</f>
+        <v>324403.52246400004</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -1549,11 +1546,11 @@
       <c r="B38" s="6"/>
       <c r="C38" s="6">
         <f>C37*0.34</f>
-        <v>33041.198794148069</v>
+        <v>26760.720000000001</v>
       </c>
       <c r="D38" s="6">
         <f>D37*0.34</f>
-        <v>33702.022770031035</v>
+        <v>27295.934400000002</v>
       </c>
       <c r="E38" s="6">
         <f>E37*0.34</f>
@@ -1565,10 +1562,7 @@
       </c>
       <c r="G38" s="24">
         <f t="shared" si="10"/>
-        <v>122983.76480193912</v>
-      </c>
-      <c r="H38" t="s">
-        <v>34</v>
+        <v>110297.19763776001</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -1594,9 +1588,6 @@
         <f t="shared" si="10"/>
         <v>140000</v>
       </c>
-      <c r="H39" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="23" t="s">
@@ -1623,7 +1614,7 @@
         <v>343507</v>
       </c>
       <c r="H40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -1671,175 +1662,198 @@
         <f t="shared" si="10"/>
         <v>80000</v>
       </c>
-      <c r="I42" s="36">
+      <c r="I42" s="33">
         <f>50000/1.39</f>
         <v>35971.223021582737</v>
       </c>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="25" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="D43" s="13">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="E43" s="13">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="F43" s="13"/>
       <c r="G43" s="26">
         <f t="shared" si="10"/>
+        <v>50000</v>
+      </c>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13">
+        <v>25000</v>
+      </c>
+      <c r="D44" s="13">
+        <v>50000</v>
+      </c>
+      <c r="E44" s="13">
+        <v>25000</v>
+      </c>
+      <c r="F44" s="13"/>
+      <c r="G44" s="26">
+        <f t="shared" si="10"/>
         <v>100000</v>
       </c>
-      <c r="I43" s="36">
+      <c r="I44" s="33">
         <f>I42*0.39</f>
         <v>14028.776978417267</v>
       </c>
-      <c r="J43" s="36"/>
-      <c r="K43" s="36"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="25" t="s">
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13">
+      <c r="B45" s="13"/>
+      <c r="C45" s="13">
         <v>60000</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D45" s="13">
         <v>60000</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E45" s="13">
         <v>60000</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F45" s="13">
         <v>60000</v>
       </c>
-      <c r="G44" s="26">
+      <c r="G45" s="26">
         <f t="shared" si="10"/>
         <v>240000</v>
       </c>
-      <c r="I44" s="36">
-        <f>SUM(I42:I43)</f>
+      <c r="I45" s="33">
+        <f>SUM(I42:I44)</f>
         <v>50000</v>
       </c>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="25" t="s">
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13">
+      <c r="B46" s="13"/>
+      <c r="C46" s="13">
         <v>0</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D46" s="13">
         <f>14999*2</f>
         <v>29998</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E46" s="13">
         <f>14999*8</f>
         <v>119992</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F46" s="13">
         <f>14999*8</f>
         <v>119992</v>
       </c>
-      <c r="G45" s="26">
+      <c r="G46" s="26">
         <f t="shared" si="10"/>
         <v>269982</v>
       </c>
-      <c r="I45" s="36">
-        <f>I44/2.02</f>
+      <c r="I46" s="33">
+        <f>I45/2.02</f>
         <v>24752.475247524751</v>
       </c>
-      <c r="J45" s="36">
-        <f>I45*1.02</f>
+      <c r="J46" s="33">
+        <f>I46*1.02</f>
         <v>25247.524752475249</v>
       </c>
-      <c r="K45" s="36">
-        <f>I45+J45</f>
+      <c r="K46" s="33">
+        <f>I46+J46</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="33" t="s">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34">
+      <c r="B47" s="31"/>
+      <c r="C47" s="31">
         <v>16000</v>
       </c>
-      <c r="D46" s="34">
+      <c r="D47" s="31">
         <v>28000</v>
       </c>
-      <c r="E46" s="34">
+      <c r="E47" s="31">
         <v>28000</v>
       </c>
-      <c r="F46" s="34">
+      <c r="F47" s="31">
         <v>28000</v>
       </c>
-      <c r="G46" s="26">
+      <c r="G47" s="26">
         <f t="shared" si="10"/>
         <v>100000</v>
       </c>
-      <c r="I46" s="36">
-        <f>I45/1.34</f>
+      <c r="I47" s="33">
+        <f>I46/1.34</f>
         <v>18471.99645337668</v>
       </c>
-      <c r="J46" s="36">
-        <f>J45/1.34</f>
+      <c r="J47" s="33">
+        <f>J46/1.34</f>
         <v>18841.436382444215</v>
       </c>
-      <c r="K46" s="36"/>
-    </row>
-    <row r="47" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="27" t="s">
+      <c r="K47" s="33"/>
+    </row>
+    <row r="48" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="28">
-        <f t="shared" ref="B47:G47" si="11">SUM(B37:B45)</f>
+      <c r="B48" s="28">
+        <f t="shared" ref="B48" si="11">SUM(B37:B46)</f>
         <v>26375</v>
       </c>
-      <c r="C47" s="28">
-        <f>SUM(C37:C46)</f>
-        <v>661221.19524752477</v>
-      </c>
-      <c r="D47" s="28">
-        <f>SUM(D37:D46)</f>
-        <v>475823.61915247526</v>
-      </c>
-      <c r="E47" s="28">
-        <f>SUM(E37:E46)</f>
-        <v>437721.656288</v>
-      </c>
-      <c r="F47" s="28">
-        <f>SUM(F37:F46)</f>
+      <c r="C48" s="28">
+        <f>SUM(C37:C47)</f>
+        <v>651468.72</v>
+      </c>
+      <c r="D48" s="28">
+        <f>SUM(D37:D47)</f>
+        <v>470576.0944</v>
+      </c>
+      <c r="E48" s="28">
+        <f>SUM(E37:E47)</f>
+        <v>452721.656288</v>
+      </c>
+      <c r="F48" s="28">
+        <f>SUM(F37:F47)</f>
         <v>411779.24941376003</v>
       </c>
-      <c r="G47" s="29">
-        <f>SUM(G37:G46)</f>
+      <c r="G48" s="29">
+        <f>SUM(G37:G47)</f>
         <v>2012920.72010176</v>
       </c>
-      <c r="H47" t="s">
-        <v>35</v>
-      </c>
-      <c r="I47" s="35">
-        <f>I46*0.34</f>
+      <c r="H48" t="s">
+        <v>34</v>
+      </c>
+      <c r="I48" s="32">
+        <f>I47*0.34</f>
         <v>6280.4787941480718</v>
       </c>
-      <c r="J47" s="35">
-        <f>J46*0.34</f>
+      <c r="J48" s="32">
+        <f>J47*0.34</f>
         <v>6406.0883700310333</v>
       </c>
-      <c r="K47" s="36"/>
+      <c r="K48" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
